--- a/results/qwen3_5_9b/comparison_CoTRAG/CoTRAG_consolidated.xlsx
+++ b/results/qwen3_5_9b/comparison_CoTRAG/CoTRAG_consolidated.xlsx
@@ -545,56 +545,58 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.01005025067144773</v>
+        <v>0.2522522473789105</v>
       </c>
       <c r="D2" t="n">
-        <v>4.112145644782141e-255</v>
+        <v>3.499347156910729e-155</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3551344275474548</v>
+        <v>0.6088988780975342</v>
       </c>
       <c r="F2" t="n">
-        <v>18.17750000000001</v>
+        <v>39.61143670886079</v>
       </c>
       <c r="G2" t="n">
-        <v>0.07757805108798486</v>
+        <v>0.7880794701986755</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
       <c r="K2" t="n">
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2</v>
+        <v>0.2377049180327869</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.3464052287581699</v>
       </c>
       <c r="N2" t="n">
-        <v>1.706821918487549</v>
+        <v>28.14152073860168</v>
       </c>
       <c r="O2" t="n">
-        <v>1420.18359375</v>
+        <v>1423.96484375</v>
       </c>
       <c r="P2" t="n">
-        <v>11.2</v>
+        <v>12.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0.349987268447876</v>
+        <v>0.6831538677215576</v>
       </c>
       <c r="T2" t="n">
-        <v>1.356829881668091</v>
+        <v>27.45836162567139</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -610,56 +612,58 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.1111111091358025</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>8.493666525496109e-232</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4478027522563934</v>
+        <v>0.5002129077911377</v>
       </c>
       <c r="F3" t="n">
-        <v>18.17750000000001</v>
+        <v>23.25551702395967</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7522935779816514</v>
+        <v>4.651376146788991</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
       <c r="K3" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2</v>
+        <v>0.3382352941176471</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2546583850931677</v>
       </c>
       <c r="N3" t="n">
-        <v>2.319665908813477</v>
+        <v>15.52196788787842</v>
       </c>
       <c r="O3" t="n">
-        <v>1420.421875</v>
+        <v>1424.18359375</v>
       </c>
       <c r="P3" t="n">
-        <v>8.9</v>
+        <v>14.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.09566617012023926</v>
+        <v>0.2805397510528564</v>
       </c>
       <c r="T3" t="n">
-        <v>2.223996162414551</v>
+        <v>15.24142456054688</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -675,56 +679,58 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>0.1984126936961452</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>2.210547689163357e-79</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2987848222255707</v>
+        <v>0.5246517658233643</v>
       </c>
       <c r="F4" t="n">
-        <v>18.17750000000001</v>
+        <v>43.48427083333334</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0876068376068376</v>
+        <v>0.5908119658119658</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
       <c r="K4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2</v>
+        <v>0.375</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.3670886075949367</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7850995063781738</v>
+        <v>12.55752444267273</v>
       </c>
       <c r="O4" t="n">
-        <v>1420.4921875</v>
+        <v>1424.30078125</v>
       </c>
       <c r="P4" t="n">
-        <v>8.4</v>
+        <v>14.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.09102272987365723</v>
+        <v>0.2421054840087891</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6940741539001465</v>
+        <v>12.31541633605957</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -740,56 +746,58 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.2399999952880001</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>4.67801905661789e-79</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2985583543777466</v>
+        <v>0.6336413621902466</v>
       </c>
       <c r="F5" t="n">
-        <v>18.17750000000001</v>
+        <v>38.72775682837343</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06710310965630115</v>
+        <v>0.6235679214402619</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
       <c r="K5" t="n">
         <v>0.5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2</v>
+        <v>0.3663366336633663</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.5121951219512195</v>
       </c>
       <c r="N5" t="n">
-        <v>1.906833410263062</v>
+        <v>13.74409937858582</v>
       </c>
       <c r="O5" t="n">
-        <v>1420.58984375</v>
+        <v>1425.84765625</v>
       </c>
       <c r="P5" t="n">
-        <v>9.5</v>
+        <v>12.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.08823752403259277</v>
+        <v>0.2770164012908936</v>
       </c>
       <c r="T5" t="n">
-        <v>1.818592548370361</v>
+        <v>13.46707987785339</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -805,56 +813,58 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.01265822711744917</v>
+        <v>0.2421524620273885</v>
       </c>
       <c r="D6" t="n">
-        <v>6.490056534318242e-251</v>
+        <v>0.0083955954548054</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3351855278015137</v>
+        <v>0.5851066112518311</v>
       </c>
       <c r="F6" t="n">
-        <v>18.17750000000001</v>
+        <v>53.62264705882353</v>
       </c>
       <c r="G6" t="n">
-        <v>0.09425287356321839</v>
+        <v>0.4804597701149425</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
       <c r="K6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.25</v>
       </c>
       <c r="N6" t="n">
-        <v>1.474850177764893</v>
+        <v>11.42347955703735</v>
       </c>
       <c r="O6" t="n">
-        <v>1420.6015625</v>
+        <v>1425.9453125</v>
       </c>
       <c r="P6" t="n">
-        <v>8.9</v>
+        <v>14.6</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.05181241035461426</v>
+        <v>0.2424299716949463</v>
       </c>
       <c r="T6" t="n">
-        <v>1.423035144805908</v>
+        <v>11.18104696273804</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -870,56 +880,58 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.004024144630681487</v>
+        <v>0.3474452514143961</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>0.007698327232697096</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3596178889274597</v>
+        <v>0.6456795930862427</v>
       </c>
       <c r="F7" t="n">
-        <v>18.17750000000001</v>
+        <v>32.8283071567358</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0238580157113762</v>
+        <v>0.3520512074483561</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
       <c r="K7" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2</v>
+        <v>0.1858974358974359</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2</v>
+        <v>0.7321428571428571</v>
       </c>
       <c r="N7" t="n">
-        <v>0.413616418838501</v>
+        <v>30.12495017051697</v>
       </c>
       <c r="O7" t="n">
-        <v>1420.68359375</v>
+        <v>1426.12890625</v>
       </c>
       <c r="P7" t="n">
-        <v>8.800000000000001</v>
+        <v>14.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.04916119575500488</v>
+        <v>0.2809305191040039</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3644523620605469</v>
+        <v>29.84401655197144</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -935,56 +947,58 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.1627118608960644</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>2.393744328776576e-157</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3447666764259338</v>
+        <v>0.5901678204536438</v>
       </c>
       <c r="F8" t="n">
-        <v>18.17750000000001</v>
+        <v>26.61927710843375</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05694444444444444</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
       <c r="K8" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M8" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1538461538461539</v>
       </c>
       <c r="N8" t="n">
-        <v>2.103248119354248</v>
+        <v>20.1275327205658</v>
       </c>
       <c r="O8" t="n">
-        <v>1420.8125</v>
+        <v>1426.25</v>
       </c>
       <c r="P8" t="n">
-        <v>17.8</v>
+        <v>13.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.05114030838012695</v>
+        <v>0.278907299041748</v>
       </c>
       <c r="T8" t="n">
-        <v>2.052104711532593</v>
+        <v>19.84862327575684</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -1000,56 +1014,58 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.006968640705605289</v>
+        <v>0.2216358800707319</v>
       </c>
       <c r="D9" t="n">
-        <v>1.940725192637606e-274</v>
+        <v>2.352199119576295e-79</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3247340321540833</v>
+        <v>0.642425537109375</v>
       </c>
       <c r="F9" t="n">
-        <v>18.17750000000001</v>
+        <v>52.66048128342248</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04750869061413673</v>
+        <v>0.3771726535341831</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.4375</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
       <c r="K9" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2</v>
+        <v>0.3647058823529412</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.3548387096774193</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4237608909606934</v>
+        <v>24.18343162536621</v>
       </c>
       <c r="O9" t="n">
-        <v>1420.8125</v>
+        <v>1426.27734375</v>
       </c>
       <c r="P9" t="n">
-        <v>17.9</v>
+        <v>14.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.04909753799438477</v>
+        <v>0.2916948795318604</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3746600151062012</v>
+        <v>23.89173412322998</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1065,56 +1081,58 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.2184154125616607</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>0.03677245973087152</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3366994261741638</v>
+        <v>0.647664487361908</v>
       </c>
       <c r="F10" t="n">
-        <v>18.17750000000001</v>
+        <v>6.092778885703638</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05423280423280423</v>
+        <v>0.9609788359788359</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
       <c r="K10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="M10" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.5358649789029536</v>
       </c>
       <c r="N10" t="n">
-        <v>2.480668067932129</v>
+        <v>34.16134881973267</v>
       </c>
       <c r="O10" t="n">
-        <v>1420.89453125</v>
+        <v>1426.40234375</v>
       </c>
       <c r="P10" t="n">
-        <v>12</v>
+        <v>15.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.120957612991333</v>
+        <v>0.2813558578491211</v>
       </c>
       <c r="T10" t="n">
-        <v>2.359707593917847</v>
+        <v>33.87999033927917</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
@@ -1130,56 +1148,58 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.006734006338128786</v>
+        <v>0.314855871253337</v>
       </c>
       <c r="D11" t="n">
-        <v>1.427007095027129e-284</v>
+        <v>0.03531317188655015</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3138718605041504</v>
+        <v>0.5857160091400146</v>
       </c>
       <c r="F11" t="n">
-        <v>18.17750000000001</v>
+        <v>57.37569230769233</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0448332422088573</v>
+        <v>0.4980863860032805</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
       <c r="K11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2</v>
+        <v>0.3257575757575757</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.494949494949495</v>
       </c>
       <c r="N11" t="n">
-        <v>1.657833337783813</v>
+        <v>17.57684969902039</v>
       </c>
       <c r="O11" t="n">
-        <v>1420.99609375</v>
+        <v>1426.50390625</v>
       </c>
       <c r="P11" t="n">
-        <v>9</v>
+        <v>12.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.04956936836242676</v>
+        <v>0.236943244934082</v>
       </c>
       <c r="T11" t="n">
-        <v>1.608261585235596</v>
+        <v>17.33990359306335</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1195,56 +1215,58 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.1949999958201251</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>9.049280421314446e-156</v>
       </c>
       <c r="E12" t="n">
-        <v>0.3342090249061584</v>
+        <v>0.6282260417938232</v>
       </c>
       <c r="F12" t="n">
-        <v>18.17750000000001</v>
+        <v>48.93568181818185</v>
       </c>
       <c r="G12" t="n">
-        <v>0.04669703872437358</v>
+        <v>0.4749430523917996</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2</v>
+        <v>0.2342342342342342</v>
       </c>
       <c r="M12" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.281437125748503</v>
       </c>
       <c r="N12" t="n">
-        <v>1.701315641403198</v>
+        <v>24.72253727912903</v>
       </c>
       <c r="O12" t="n">
-        <v>1421.04296875</v>
+        <v>1426.5234375</v>
       </c>
       <c r="P12" t="n">
-        <v>9.5</v>
+        <v>14.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.04933333396911621</v>
+        <v>0.2424871921539307</v>
       </c>
       <c r="T12" t="n">
-        <v>1.651979446411133</v>
+        <v>24.48004722595215</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1260,56 +1282,58 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.006622516166834812</v>
+        <v>0.169863010632539</v>
       </c>
       <c r="D13" t="n">
-        <v>1.848714805888607e-281</v>
+        <v>1.138729583003279e-80</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3324247598648071</v>
+        <v>0.6448227763175964</v>
       </c>
       <c r="F13" t="n">
-        <v>18.17750000000001</v>
+        <v>59.65907721280604</v>
       </c>
       <c r="G13" t="n">
-        <v>0.04545454545454546</v>
+        <v>0.2361419068736142</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>0.35</v>
       </c>
       <c r="I13" t="n">
         <v>1</v>
       </c>
-      <c r="J13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2</v>
+        <v>0.3018867924528302</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2783505154639175</v>
       </c>
       <c r="N13" t="n">
-        <v>2.509064912796021</v>
+        <v>17.93367052078247</v>
       </c>
       <c r="O13" t="n">
-        <v>1421.11328125</v>
+        <v>1426.52734375</v>
       </c>
       <c r="P13" t="n">
-        <v>9</v>
+        <v>14.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0.05124020576477051</v>
+        <v>0.2536413669586182</v>
       </c>
       <c r="T13" t="n">
-        <v>2.457822322845459</v>
+        <v>17.68002653121948</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -1325,56 +1349,58 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.1792618579192678</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>0.01263108921430186</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3325183093547821</v>
+        <v>0.6010398864746094</v>
       </c>
       <c r="F14" t="n">
-        <v>18.17750000000001</v>
+        <v>2.960311004784728</v>
       </c>
       <c r="G14" t="n">
-        <v>0.04555555555555556</v>
+        <v>0.9288888888888889</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
       <c r="K14" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2</v>
+        <v>0.2023809523809524</v>
       </c>
       <c r="M14" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.5679012345679012</v>
       </c>
       <c r="N14" t="n">
-        <v>1.387258291244507</v>
+        <v>42.45850825309753</v>
       </c>
       <c r="O14" t="n">
-        <v>1421.19921875</v>
+        <v>1426.58984375</v>
       </c>
       <c r="P14" t="n">
-        <v>9</v>
+        <v>14.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.05224132537841797</v>
+        <v>0.23722243309021</v>
       </c>
       <c r="T14" t="n">
-        <v>1.335014581680298</v>
+        <v>42.22128295898438</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1390,56 +1416,58 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.2782608646502836</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>3.50839260170082e-155</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3425537645816803</v>
+        <v>0.7033020257949829</v>
       </c>
       <c r="F15" t="n">
-        <v>18.17750000000001</v>
+        <v>38.87717922077925</v>
       </c>
       <c r="G15" t="n">
-        <v>0.164989939637827</v>
+        <v>1.702213279678068</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2</v>
+        <v>0.2929292929292929</v>
       </c>
       <c r="M15" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.3469387755102041</v>
       </c>
       <c r="N15" t="n">
-        <v>2.518002033233643</v>
+        <v>21.11018228530884</v>
       </c>
       <c r="O15" t="n">
-        <v>1421.24609375</v>
+        <v>1426.671875</v>
       </c>
       <c r="P15" t="n">
-        <v>15.3</v>
+        <v>14.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.05099248886108398</v>
+        <v>0.2437012195587158</v>
       </c>
       <c r="T15" t="n">
-        <v>2.467007398605347</v>
+        <v>20.86647796630859</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1455,56 +1483,58 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.2671480094639576</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>0.06554648452824906</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3363480567932129</v>
+        <v>0.6893495917320251</v>
       </c>
       <c r="F16" t="n">
-        <v>18.17750000000001</v>
+        <v>42.42375920810315</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1169757489300999</v>
+        <v>1.369472182596291</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
       <c r="K16" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>0.2</v>
+        <v>0.2935779816513762</v>
       </c>
       <c r="M16" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.3801652892561983</v>
       </c>
       <c r="N16" t="n">
-        <v>1.026593208312988</v>
+        <v>31.17437195777893</v>
       </c>
       <c r="O16" t="n">
-        <v>1421.24609375</v>
+        <v>1426.703125</v>
       </c>
       <c r="P16" t="n">
-        <v>18.4</v>
+        <v>14.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0.05089664459228516</v>
+        <v>0.2448248863220215</v>
       </c>
       <c r="T16" t="n">
-        <v>0.9756934642791748</v>
+        <v>30.92954397201538</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -1520,56 +1550,58 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.2450142402805173</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>7.644460866191573e-79</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3349585831165314</v>
+        <v>0.6701482534408569</v>
       </c>
       <c r="F17" t="n">
-        <v>18.17750000000001</v>
+        <v>55.32170203359863</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1102150537634409</v>
+        <v>1.827956989247312</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
       <c r="K17" t="n">
         <v>0.5</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2</v>
+        <v>0.2847682119205298</v>
       </c>
       <c r="M17" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.5736434108527132</v>
       </c>
       <c r="N17" t="n">
-        <v>1.281811714172363</v>
+        <v>45.16979837417603</v>
       </c>
       <c r="O17" t="n">
-        <v>1421.24609375</v>
+        <v>1426.796875</v>
       </c>
       <c r="P17" t="n">
-        <v>11.3</v>
+        <v>14.6</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.05534815788269043</v>
+        <v>0.2408351898193359</v>
       </c>
       <c r="T17" t="n">
-        <v>1.226461172103882</v>
+        <v>44.92896103858948</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1585,56 +1617,58 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>0.3116057187144912</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>0.1019237140176351</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3638949990272522</v>
+        <v>0.6736286878585815</v>
       </c>
       <c r="F18" t="n">
-        <v>18.17750000000001</v>
+        <v>57.00158730158731</v>
       </c>
       <c r="G18" t="n">
-        <v>0.03193146417445483</v>
+        <v>0.6304517133956387</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
       <c r="K18" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2</v>
+        <v>0.2611111111111111</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.5780590717299579</v>
       </c>
       <c r="N18" t="n">
-        <v>1.795159578323364</v>
+        <v>30.74105763435364</v>
       </c>
       <c r="O18" t="n">
-        <v>1421.25</v>
+        <v>1426.875</v>
       </c>
       <c r="P18" t="n">
-        <v>9</v>
+        <v>14.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.04862594604492188</v>
+        <v>0.2813055515289307</v>
       </c>
       <c r="T18" t="n">
-        <v>1.746531009674072</v>
+        <v>30.4597499370575</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -1650,56 +1684,58 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>0.1245901607739856</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>2.274367346849618e-81</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3354047536849976</v>
+        <v>0.6037366986274719</v>
       </c>
       <c r="F19" t="n">
-        <v>18.17750000000001</v>
+        <v>19.49400000000003</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05405405405405406</v>
+        <v>0.2491760052735663</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.2352941176470588</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
       <c r="K19" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2</v>
+        <v>0.3018867924528302</v>
       </c>
       <c r="M19" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.1240875912408759</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4386868476867676</v>
+        <v>16.41390299797058</v>
       </c>
       <c r="O19" t="n">
-        <v>1421.328125</v>
+        <v>1426.9453125</v>
       </c>
       <c r="P19" t="n">
-        <v>9.300000000000001</v>
+        <v>14.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.04829859733581543</v>
+        <v>0.2434377670288086</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3903858661651611</v>
+        <v>16.1704626083374</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -1715,56 +1751,58 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.007999999531520028</v>
+        <v>0.2670623105438985</v>
       </c>
       <c r="D20" t="n">
-        <v>2.011151139993215e-262</v>
+        <v>3.01248324859832e-79</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3511017560958862</v>
+        <v>0.6838187575340271</v>
       </c>
       <c r="F20" t="n">
-        <v>18.17750000000001</v>
+        <v>55.89562500000002</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05819730305180979</v>
+        <v>0.4109297374024131</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>0.625</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
       <c r="K20" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2</v>
+        <v>0.3291139240506329</v>
       </c>
       <c r="M20" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.2073170731707317</v>
       </c>
       <c r="N20" t="n">
-        <v>1.664188623428345</v>
+        <v>18.79751110076904</v>
       </c>
       <c r="O20" t="n">
-        <v>1421.3359375</v>
+        <v>1427.02734375</v>
       </c>
       <c r="P20" t="n">
-        <v>9.1</v>
+        <v>13.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.04989814758300781</v>
+        <v>0.2724058628082275</v>
       </c>
       <c r="T20" t="n">
-        <v>1.614287853240967</v>
+        <v>18.52510261535645</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -1780,56 +1818,58 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>0.1603665479552675</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>7.254289863126926e-79</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3511861562728882</v>
+        <v>0.5893725156784058</v>
       </c>
       <c r="F21" t="n">
-        <v>18.17750000000001</v>
+        <v>30.91215960779397</v>
       </c>
       <c r="G21" t="n">
-        <v>0.04645892351274788</v>
+        <v>2.705949008498584</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
       <c r="K21" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2</v>
+        <v>0.1399082568807339</v>
       </c>
       <c r="M21" t="n">
-        <v>0.01408450704225352</v>
+        <v>0.4888408927285818</v>
       </c>
       <c r="N21" t="n">
-        <v>0.6557137966156006</v>
+        <v>120.5542068481445</v>
       </c>
       <c r="O21" t="n">
-        <v>1421.60546875</v>
+        <v>1427.18359375</v>
       </c>
       <c r="P21" t="n">
-        <v>9.1</v>
+        <v>15</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.05228066444396973</v>
+        <v>0.3165504932403564</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6034309864044189</v>
+        <v>120.2376534938812</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -1845,56 +1885,58 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.3862068917003567</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>0.06653561603462374</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3543737828731537</v>
+        <v>0.6371625661849976</v>
       </c>
       <c r="F22" t="n">
-        <v>18.17750000000001</v>
+        <v>44.7641090425532</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0496969696969697</v>
+        <v>0.6739393939393939</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
       <c r="K22" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2</v>
+        <v>0.3087248322147651</v>
       </c>
       <c r="M22" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.3658536585365854</v>
       </c>
       <c r="N22" t="n">
-        <v>1.696043014526367</v>
+        <v>23.7665798664093</v>
       </c>
       <c r="O22" t="n">
-        <v>1421.6640625</v>
+        <v>1427.21484375</v>
       </c>
       <c r="P22" t="n">
-        <v>9.199999999999999</v>
+        <v>14.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.04996848106384277</v>
+        <v>1.423193454742432</v>
       </c>
       <c r="T22" t="n">
-        <v>1.646071910858154</v>
+        <v>22.3433837890625</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -1910,56 +1952,58 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.005830903446353156</v>
+        <v>0.1088082879388709</v>
       </c>
       <c r="D23" t="n">
-        <v>8.881898537364234e-295</v>
+        <v>2.300145208636924e-07</v>
       </c>
       <c r="E23" t="n">
-        <v>0.354942262172699</v>
+        <v>0.5175822377204895</v>
       </c>
       <c r="F23" t="n">
-        <v>18.17750000000001</v>
+        <v>27.77803225806454</v>
       </c>
       <c r="G23" t="n">
-        <v>0.03766651355075792</v>
+        <v>0.1423977951309141</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
       <c r="K23" t="n">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2</v>
+        <v>0.3488372093023256</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="N23" t="n">
-        <v>1.673414468765259</v>
+        <v>20.15850138664246</v>
       </c>
       <c r="O23" t="n">
-        <v>1421.6796875</v>
+        <v>1427.23046875</v>
       </c>
       <c r="P23" t="n">
-        <v>8.9</v>
+        <v>13.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0524594783782959</v>
+        <v>0.2364990711212158</v>
       </c>
       <c r="T23" t="n">
-        <v>1.620952844619751</v>
+        <v>19.92199993133545</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -1975,56 +2019,58 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.2511627857029747</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>0.02558259669607099</v>
       </c>
       <c r="E24" t="n">
-        <v>0.3240000605583191</v>
+        <v>0.6294016242027283</v>
       </c>
       <c r="F24" t="n">
-        <v>18.17750000000001</v>
+        <v>44.19869318181821</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1259600614439324</v>
+        <v>1.096774193548387</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
       <c r="K24" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>0.2</v>
+        <v>0.2842105263157895</v>
       </c>
       <c r="M24" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.3048128342245989</v>
       </c>
       <c r="N24" t="n">
-        <v>1.170245409011841</v>
+        <v>18.35392165184021</v>
       </c>
       <c r="O24" t="n">
-        <v>1421.75</v>
+        <v>1427.2890625</v>
       </c>
       <c r="P24" t="n">
-        <v>10.4</v>
+        <v>13.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0.04999351501464844</v>
+        <v>0.2829515933990479</v>
       </c>
       <c r="T24" t="n">
-        <v>1.12024998664856</v>
+        <v>18.07096767425537</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2040,56 +2086,58 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>0.2352941137852963</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>1.777798808715947e-79</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3377845585346222</v>
+        <v>0.5950129628181458</v>
       </c>
       <c r="F25" t="n">
-        <v>18.17750000000001</v>
+        <v>52.245</v>
       </c>
       <c r="G25" t="n">
-        <v>0.1236802413273002</v>
+        <v>0.4012066365007542</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
       <c r="K25" t="n">
         <v>0.5</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2</v>
+        <v>0.2121212121212121</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1549295774647887</v>
       </c>
       <c r="N25" t="n">
-        <v>1.458403587341309</v>
+        <v>9.765125513076782</v>
       </c>
       <c r="O25" t="n">
-        <v>1421.75390625</v>
+        <v>1427.31640625</v>
       </c>
       <c r="P25" t="n">
-        <v>18.6</v>
+        <v>15.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0.04906821250915527</v>
+        <v>0.240358829498291</v>
       </c>
       <c r="T25" t="n">
-        <v>1.409332752227783</v>
+        <v>9.524764537811279</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2105,56 +2153,58 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>0.2550335524255665</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1.526247344882286e-155</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3307645320892334</v>
+        <v>0.6127455234527588</v>
       </c>
       <c r="F26" t="n">
-        <v>18.17750000000001</v>
+        <v>48.24250000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1421143847487002</v>
+        <v>0.5805892547660312</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
       <c r="K26" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L26" t="n">
+        <v>0.2272727272727273</v>
+      </c>
+      <c r="M26" t="n">
         <v>0.2</v>
       </c>
-      <c r="M26" t="n">
-        <v>0.1428571428571428</v>
-      </c>
       <c r="N26" t="n">
-        <v>1.465075492858887</v>
+        <v>11.67943692207336</v>
       </c>
       <c r="O26" t="n">
-        <v>1421.75390625</v>
+        <v>1427.31640625</v>
       </c>
       <c r="P26" t="n">
-        <v>18.6</v>
+        <v>12.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.05169343948364258</v>
+        <v>0.2349963188171387</v>
       </c>
       <c r="T26" t="n">
-        <v>1.413379430770874</v>
+        <v>11.44443774223328</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -2170,56 +2220,58 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>0.2499999959820507</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>0.01362079073436029</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3288788795471191</v>
+        <v>0.5358278155326843</v>
       </c>
       <c r="F27" t="n">
-        <v>18.17750000000001</v>
+        <v>53.35593530239103</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1121751025991792</v>
+        <v>0.4322845417236662</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
       <c r="K27" t="n">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>0.2</v>
+        <v>0.3181818181818182</v>
       </c>
       <c r="M27" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2424242424242424</v>
       </c>
       <c r="N27" t="n">
-        <v>1.524911165237427</v>
+        <v>11.11807060241699</v>
       </c>
       <c r="O27" t="n">
-        <v>1421.7578125</v>
+        <v>1427.37109375</v>
       </c>
       <c r="P27" t="n">
-        <v>8.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0.09921360015869141</v>
+        <v>0.2414374351501465</v>
       </c>
       <c r="T27" t="n">
-        <v>1.425694942474365</v>
+        <v>10.8766303062439</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2235,56 +2287,58 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>0.2456140306049726</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>5.860576509947883e-79</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3372243940830231</v>
+        <v>0.6032034158706665</v>
       </c>
       <c r="F28" t="n">
-        <v>18.17750000000001</v>
+        <v>48.12750000000003</v>
       </c>
       <c r="G28" t="n">
-        <v>0.1242424242424242</v>
+        <v>0.5590909090909091</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
       <c r="K28" t="n">
         <v>0.5</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2</v>
+        <v>0.2826086956521739</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="N28" t="n">
-        <v>0.510322093963623</v>
+        <v>11.24601626396179</v>
       </c>
       <c r="O28" t="n">
-        <v>1421.76171875</v>
+        <v>1427.40625</v>
       </c>
       <c r="P28" t="n">
-        <v>8.9</v>
+        <v>14.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0.04949498176574707</v>
+        <v>0.2954463958740234</v>
       </c>
       <c r="T28" t="n">
-        <v>0.4608244895935059</v>
+        <v>10.9505672454834</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -2300,56 +2354,58 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>0.2823529362456748</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>2.97772255365967e-155</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3312129080295563</v>
+        <v>0.6508529186248779</v>
       </c>
       <c r="F29" t="n">
-        <v>18.17750000000001</v>
+        <v>52.74738700564976</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1423611111111111</v>
+        <v>0.828125</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
       <c r="K29" t="n">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>0.2</v>
+        <v>0.3389830508474576</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="N29" t="n">
-        <v>1.419867753982544</v>
+        <v>14.36031126976013</v>
       </c>
       <c r="O29" t="n">
-        <v>1421.77734375</v>
+        <v>1427.48046875</v>
       </c>
       <c r="P29" t="n">
-        <v>9.300000000000001</v>
+        <v>12.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0.04925251007080078</v>
+        <v>0.2365856170654297</v>
       </c>
       <c r="T29" t="n">
-        <v>1.370613574981689</v>
+        <v>14.12372279167175</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -2365,56 +2421,58 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>0.07999999788800007</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>2.086816969704057e-155</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4661099910736084</v>
+        <v>0.4730966985225677</v>
       </c>
       <c r="F30" t="n">
-        <v>18.17750000000001</v>
+        <v>31.37374269005852</v>
       </c>
       <c r="G30" t="n">
-        <v>0.82</v>
+        <v>4.48</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
       <c r="K30" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>0.2</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="M30" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2156862745098039</v>
       </c>
       <c r="N30" t="n">
-        <v>1.292150735855103</v>
+        <v>12.9955415725708</v>
       </c>
       <c r="O30" t="n">
-        <v>1421.7890625</v>
+        <v>1427.52734375</v>
       </c>
       <c r="P30" t="n">
-        <v>8.9</v>
+        <v>14.4</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0.04937362670898438</v>
+        <v>0.2415950298309326</v>
       </c>
       <c r="T30" t="n">
-        <v>1.24277400970459</v>
+        <v>12.75394439697266</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -2430,56 +2488,58 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.05517241262877529</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>1.392503783826371e-155</v>
       </c>
       <c r="E31" t="n">
-        <v>0.4586723148822784</v>
+        <v>0.4471685588359833</v>
       </c>
       <c r="F31" t="n">
-        <v>18.17750000000001</v>
+        <v>29.74105263157898</v>
       </c>
       <c r="G31" t="n">
-        <v>0.7961165048543689</v>
+        <v>8.58252427184466</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
       <c r="K31" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>0.2</v>
+        <v>0.3482142857142857</v>
       </c>
       <c r="M31" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.3415637860082305</v>
       </c>
       <c r="N31" t="n">
-        <v>2.377240419387817</v>
+        <v>23.65238189697266</v>
       </c>
       <c r="O31" t="n">
-        <v>1421.81640625</v>
+        <v>1427.54296875</v>
       </c>
       <c r="P31" t="n">
-        <v>8.6</v>
+        <v>14.9</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0.1925017833709717</v>
+        <v>0.2395443916320801</v>
       </c>
       <c r="T31" t="n">
-        <v>2.184736013412476</v>
+        <v>23.41283512115479</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -2495,56 +2555,58 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.1290322555827264</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>2.668419795632472e-155</v>
       </c>
       <c r="E32" t="n">
-        <v>0.4568907618522644</v>
+        <v>0.5000985264778137</v>
       </c>
       <c r="F32" t="n">
-        <v>18.17750000000001</v>
+        <v>42.54500000000002</v>
       </c>
       <c r="G32" t="n">
-        <v>0.82</v>
+        <v>3.12</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
       <c r="K32" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="L32" t="n">
-        <v>0.2</v>
+        <v>0.2608695652173913</v>
       </c>
       <c r="M32" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.1071428571428571</v>
       </c>
       <c r="N32" t="n">
-        <v>1.714750528335571</v>
+        <v>13.19795632362366</v>
       </c>
       <c r="O32" t="n">
-        <v>1421.82421875</v>
+        <v>1427.54296875</v>
       </c>
       <c r="P32" t="n">
-        <v>9.199999999999999</v>
+        <v>12.6</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0.05134940147399902</v>
+        <v>0.2682473659515381</v>
       </c>
       <c r="T32" t="n">
-        <v>1.663398742675781</v>
+        <v>12.92970585823059</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -2560,56 +2622,58 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.1830985868706607</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>8.67426708862619e-79</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4066851437091827</v>
+        <v>0.6039671301841736</v>
       </c>
       <c r="F33" t="n">
-        <v>18.17750000000001</v>
+        <v>64.40200000000002</v>
       </c>
       <c r="G33" t="n">
-        <v>0.2271468144044321</v>
+        <v>1.484764542936288</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L33" t="n">
-        <v>0.2</v>
+        <v>0.3380281690140845</v>
       </c>
       <c r="M33" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.2592592592592593</v>
       </c>
       <c r="N33" t="n">
-        <v>1.115107536315918</v>
+        <v>24.24566864967346</v>
       </c>
       <c r="O33" t="n">
-        <v>1421.95703125</v>
+        <v>1427.5625</v>
       </c>
       <c r="P33" t="n">
-        <v>10.4</v>
+        <v>14.9</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0.0502772331237793</v>
+        <v>0.2397534847259521</v>
       </c>
       <c r="T33" t="n">
-        <v>1.064826726913452</v>
+        <v>24.00591349601746</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -2625,56 +2689,58 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.1546961280583622</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>1.331703150371593e-155</v>
       </c>
       <c r="E34" t="n">
-        <v>0.387653112411499</v>
+        <v>0.5606230497360229</v>
       </c>
       <c r="F34" t="n">
-        <v>18.17750000000001</v>
+        <v>59.32328571428573</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1191860465116279</v>
+        <v>0.5494186046511628</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
       <c r="K34" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="M34" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2173913043478261</v>
       </c>
       <c r="N34" t="n">
-        <v>1.966100215911865</v>
+        <v>17.30383276939392</v>
       </c>
       <c r="O34" t="n">
-        <v>1422.01171875</v>
+        <v>1427.5703125</v>
       </c>
       <c r="P34" t="n">
-        <v>18.4</v>
+        <v>14</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>0.05168390274047852</v>
+        <v>0.2415008544921875</v>
       </c>
       <c r="T34" t="n">
-        <v>1.914413690567017</v>
+        <v>17.06232929229736</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -2690,56 +2756,58 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.2833787416296803</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>0.06787718494567502</v>
       </c>
       <c r="E35" t="n">
-        <v>0.3536517918109894</v>
+        <v>0.6573120951652527</v>
       </c>
       <c r="F35" t="n">
-        <v>18.17750000000001</v>
+        <v>25.80440384615386</v>
       </c>
       <c r="G35" t="n">
-        <v>0.07180385288966724</v>
+        <v>0.9395796847635727</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
       <c r="K35" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2</v>
+        <v>0.3170731707317073</v>
       </c>
       <c r="M35" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.3548387096774193</v>
       </c>
       <c r="N35" t="n">
-        <v>0.8537487983703613</v>
+        <v>30.63400864601135</v>
       </c>
       <c r="O35" t="n">
-        <v>1422.0234375</v>
+        <v>1427.64453125</v>
       </c>
       <c r="P35" t="n">
-        <v>18.9</v>
+        <v>14.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0.05187606811523438</v>
+        <v>0.2347116470336914</v>
       </c>
       <c r="T35" t="n">
-        <v>0.8018703460693359</v>
+        <v>30.39929342269897</v>
       </c>
       <c r="U35" t="n">
         <v>0</v>
@@ -2755,56 +2823,58 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.2408376916378389</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>2.673284978658312e-155</v>
       </c>
       <c r="E36" t="n">
-        <v>0.3259139358997345</v>
+        <v>0.5875635147094727</v>
       </c>
       <c r="F36" t="n">
-        <v>18.17750000000001</v>
+        <v>43.2726015037594</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1299524564183835</v>
+        <v>0.820919175911252</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
       <c r="K36" t="n">
         <v>1</v>
       </c>
       <c r="L36" t="n">
-        <v>0.2</v>
+        <v>0.2698412698412698</v>
       </c>
       <c r="M36" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.28</v>
       </c>
       <c r="N36" t="n">
-        <v>1.162926197052002</v>
+        <v>19.29005217552185</v>
       </c>
       <c r="O36" t="n">
-        <v>1422.046875</v>
+        <v>1427.671875</v>
       </c>
       <c r="P36" t="n">
-        <v>9.199999999999999</v>
+        <v>13.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0.05158853530883789</v>
+        <v>0.2424337863922119</v>
       </c>
       <c r="T36" t="n">
-        <v>1.111335039138794</v>
+        <v>19.04761600494385</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -2820,56 +2890,58 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.2139037384529155</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>5.974857919522055e-79</v>
       </c>
       <c r="E37" t="n">
-        <v>0.3582238852977753</v>
+        <v>0.6419708132743835</v>
       </c>
       <c r="F37" t="n">
-        <v>18.17750000000001</v>
+        <v>61.02199999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>0.08695652173913043</v>
+        <v>1.343584305408271</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
       <c r="K37" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0.2</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="M37" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.5192307692307693</v>
       </c>
       <c r="N37" t="n">
-        <v>2.302383422851562</v>
+        <v>38.33541822433472</v>
       </c>
       <c r="O37" t="n">
-        <v>1422.0625</v>
+        <v>1427.78125</v>
       </c>
       <c r="P37" t="n">
-        <v>9</v>
+        <v>14.9</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0.04957008361816406</v>
+        <v>0.2810478210449219</v>
       </c>
       <c r="T37" t="n">
-        <v>2.252810955047607</v>
+        <v>38.05436754226685</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -2885,56 +2957,58 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.2666666616801098</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
+        <v>3.503348170824588e-155</v>
       </c>
       <c r="E38" t="n">
-        <v>0.3600032925605774</v>
+        <v>0.6014745831489563</v>
       </c>
       <c r="F38" t="n">
-        <v>18.17750000000001</v>
+        <v>29.37976090225567</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1060802069857697</v>
+        <v>1.14359637774903</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
       <c r="K38" t="n">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>0.2</v>
+        <v>0.2457627118644068</v>
       </c>
       <c r="M38" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.4346289752650176</v>
       </c>
       <c r="N38" t="n">
-        <v>1.948634624481201</v>
+        <v>29.98873829841614</v>
       </c>
       <c r="O38" t="n">
-        <v>1422.14453125</v>
+        <v>1427.79296875</v>
       </c>
       <c r="P38" t="n">
-        <v>9.300000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>0.04948115348815918</v>
+        <v>0.2354922294616699</v>
       </c>
       <c r="T38" t="n">
-        <v>1.899151086807251</v>
+        <v>29.75324296951294</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -2950,56 +3024,58 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.2008733574531379</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>3.839245936998267e-155</v>
       </c>
       <c r="E39" t="n">
-        <v>0.3516546189785004</v>
+        <v>0.6582720279693604</v>
       </c>
       <c r="F39" t="n">
-        <v>18.17750000000001</v>
+        <v>34.98882322175734</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1209439528023599</v>
+        <v>1.269911504424779</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="M39" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.4190871369294605</v>
       </c>
       <c r="N39" t="n">
-        <v>1.577873945236206</v>
+        <v>23.14711952209473</v>
       </c>
       <c r="O39" t="n">
-        <v>1422.1484375</v>
+        <v>1427.82421875</v>
       </c>
       <c r="P39" t="n">
-        <v>9.199999999999999</v>
+        <v>14.1</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>0.04948902130126953</v>
+        <v>0.241112232208252</v>
       </c>
       <c r="T39" t="n">
-        <v>1.528383255004883</v>
+        <v>22.9060046672821</v>
       </c>
       <c r="U39" t="n">
         <v>0</v>
@@ -3015,56 +3091,58 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.2131147494423543</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>0.01480003679540396</v>
       </c>
       <c r="E40" t="n">
-        <v>0.2961157560348511</v>
+        <v>0.5546265244483948</v>
       </c>
       <c r="F40" t="n">
-        <v>18.17750000000001</v>
+        <v>53.72872302158277</v>
       </c>
       <c r="G40" t="n">
-        <v>0.09030837004405286</v>
+        <v>0.5947136563876652</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
         <v>1</v>
       </c>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
       <c r="K40" t="n">
         <v>0.5</v>
       </c>
       <c r="L40" t="n">
-        <v>0.2</v>
+        <v>0.3661971830985916</v>
       </c>
       <c r="M40" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.3670886075949367</v>
       </c>
       <c r="N40" t="n">
-        <v>0.5440893173217773</v>
+        <v>12.27740526199341</v>
       </c>
       <c r="O40" t="n">
-        <v>1422.16015625</v>
+        <v>1427.88671875</v>
       </c>
       <c r="P40" t="n">
-        <v>8.9</v>
+        <v>14</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0.04987859725952148</v>
+        <v>0.2815837860107422</v>
       </c>
       <c r="T40" t="n">
-        <v>0.4942085742950439</v>
+        <v>11.9958188533783</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -3080,56 +3158,58 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.2349397554412833</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>0.001934249399250621</v>
       </c>
       <c r="E41" t="n">
-        <v>0.2989104390144348</v>
+        <v>0.6642762422561646</v>
       </c>
       <c r="F41" t="n">
-        <v>18.17750000000001</v>
+        <v>53.29224137931038</v>
       </c>
       <c r="G41" t="n">
-        <v>0.05624142661179699</v>
+        <v>0.3106995884773662</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I41" t="n">
         <v>1</v>
       </c>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
       <c r="K41" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>0.2</v>
+        <v>0.293103448275862</v>
       </c>
       <c r="M41" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2682926829268293</v>
       </c>
       <c r="N41" t="n">
-        <v>1.611111640930176</v>
+        <v>12.31471705436707</v>
       </c>
       <c r="O41" t="n">
-        <v>1422.16015625</v>
+        <v>1427.91015625</v>
       </c>
       <c r="P41" t="n">
-        <v>9.199999999999999</v>
+        <v>13.6</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>0.04964447021484375</v>
+        <v>0.2349236011505127</v>
       </c>
       <c r="T41" t="n">
-        <v>1.561464786529541</v>
+        <v>12.07979106903076</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -3145,56 +3225,58 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.01265822711744917</v>
+        <v>0.3003952521201707</v>
       </c>
       <c r="D42" t="n">
-        <v>6.490056534318242e-251</v>
+        <v>0.02706927422718192</v>
       </c>
       <c r="E42" t="n">
-        <v>0.3356978297233582</v>
+        <v>0.6386897563934326</v>
       </c>
       <c r="F42" t="n">
-        <v>18.17750000000001</v>
+        <v>45.84807692307695</v>
       </c>
       <c r="G42" t="n">
-        <v>0.09371428571428571</v>
+        <v>0.64</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I42" t="n">
         <v>1</v>
       </c>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
       <c r="K42" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L42" t="n">
-        <v>0.2</v>
+        <v>0.2763157894736842</v>
       </c>
       <c r="M42" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.2660550458715596</v>
       </c>
       <c r="N42" t="n">
-        <v>2.062058925628662</v>
+        <v>15.83804440498352</v>
       </c>
       <c r="O42" t="n">
-        <v>1422.21484375</v>
+        <v>1427.9140625</v>
       </c>
       <c r="P42" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>0.0497279167175293</v>
+        <v>0.2399337291717529</v>
       </c>
       <c r="T42" t="n">
-        <v>2.012328147888184</v>
+        <v>15.59810781478882</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -3210,56 +3292,58 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.1687763672523991</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>0.01328845794961592</v>
       </c>
       <c r="E43" t="n">
-        <v>0.362062394618988</v>
+        <v>0.6505063772201538</v>
       </c>
       <c r="F43" t="n">
-        <v>18.17750000000001</v>
+        <v>33.69680000000002</v>
       </c>
       <c r="G43" t="n">
-        <v>0.07599629286376275</v>
+        <v>0.4179796107506951</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
       <c r="K43" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>0.2</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="M43" t="n">
-        <v>0.02564102564102564</v>
+        <v>0.1093117408906883</v>
       </c>
       <c r="N43" t="n">
-        <v>1.796472787857056</v>
+        <v>16.69436430931091</v>
       </c>
       <c r="O43" t="n">
-        <v>1422.296875</v>
+        <v>1427.91796875</v>
       </c>
       <c r="P43" t="n">
-        <v>18.4</v>
+        <v>14.2</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0.05265164375305176</v>
+        <v>0.2610995769500732</v>
       </c>
       <c r="T43" t="n">
-        <v>1.743818759918213</v>
+        <v>16.43326163291931</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -3275,56 +3359,58 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.2307692259829189</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>0.02954706514525277</v>
       </c>
       <c r="E44" t="n">
-        <v>0.3328955769538879</v>
+        <v>0.7008967995643616</v>
       </c>
       <c r="F44" t="n">
-        <v>18.17750000000001</v>
+        <v>46.00980134538577</v>
       </c>
       <c r="G44" t="n">
-        <v>0.09414466130884042</v>
+        <v>1.812858783008037</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L44" t="n">
-        <v>0.2</v>
+        <v>0.2736842105263158</v>
       </c>
       <c r="M44" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.4164456233421751</v>
       </c>
       <c r="N44" t="n">
-        <v>0.4024243354797363</v>
+        <v>35.15044331550598</v>
       </c>
       <c r="O44" t="n">
-        <v>1422.37890625</v>
+        <v>1427.96484375</v>
       </c>
       <c r="P44" t="n">
-        <v>9.1</v>
+        <v>14.3</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0.05441999435424805</v>
+        <v>0.2733922004699707</v>
       </c>
       <c r="T44" t="n">
-        <v>0.3480007648468018</v>
+        <v>34.87704825401306</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -3340,56 +3426,58 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.3560606015045659</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>0.06324353063451552</v>
       </c>
       <c r="E45" t="n">
-        <v>0.36503866314888</v>
+        <v>0.6307464241981506</v>
       </c>
       <c r="F45" t="n">
-        <v>18.17750000000001</v>
+        <v>38.8847407229577</v>
       </c>
       <c r="G45" t="n">
-        <v>0.02248423361667124</v>
+        <v>0.6133808609816287</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.5</v>
+      </c>
       <c r="K45" t="n">
         <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>0.2</v>
+        <v>0.2711864406779661</v>
       </c>
       <c r="M45" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.6099290780141844</v>
       </c>
       <c r="N45" t="n">
-        <v>1.285399675369263</v>
+        <v>51.59527850151062</v>
       </c>
       <c r="O45" t="n">
-        <v>1422.40625</v>
+        <v>1428.03515625</v>
       </c>
       <c r="P45" t="n">
-        <v>8.9</v>
+        <v>14.9</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>0.04978108406066895</v>
+        <v>0.240816593170166</v>
       </c>
       <c r="T45" t="n">
-        <v>1.235615253448486</v>
+        <v>51.35445880889893</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
@@ -3405,56 +3493,58 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.1975683862329431</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>0.0009735805746158158</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3502118289470673</v>
+        <v>0.6121154427528381</v>
       </c>
       <c r="F46" t="n">
-        <v>18.17750000000001</v>
+        <v>58.51630945679707</v>
       </c>
       <c r="G46" t="n">
-        <v>0.02270839102741623</v>
+        <v>0.185267238991969</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>0.3571428571428572</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
       <c r="K46" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>0.2</v>
+        <v>0.2906976744186047</v>
       </c>
       <c r="M46" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.4845360824742268</v>
       </c>
       <c r="N46" t="n">
-        <v>1.114473581314087</v>
+        <v>23.64381003379822</v>
       </c>
       <c r="O46" t="n">
-        <v>1422.4140625</v>
+        <v>1428.10546875</v>
       </c>
       <c r="P46" t="n">
-        <v>9</v>
+        <v>14.8</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>0.04797625541687012</v>
+        <v>0.2393677234649658</v>
       </c>
       <c r="T46" t="n">
-        <v>1.066495180130005</v>
+        <v>23.40443968772888</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -3470,56 +3560,58 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.3213610545381128</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>0.0243251300372438</v>
       </c>
       <c r="E47" t="n">
-        <v>0.3643769919872284</v>
+        <v>0.6501205563545227</v>
       </c>
       <c r="F47" t="n">
-        <v>18.17750000000001</v>
+        <v>30.54264941498897</v>
       </c>
       <c r="G47" t="n">
-        <v>0.03268234356317258</v>
+        <v>0.4228776404942208</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
       <c r="K47" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L47" t="n">
-        <v>0.2</v>
+        <v>0.3025210084033613</v>
       </c>
       <c r="M47" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="N47" t="n">
-        <v>1.099425077438354</v>
+        <v>29.54692220687866</v>
       </c>
       <c r="O47" t="n">
-        <v>1422.43359375</v>
+        <v>1428.20703125</v>
       </c>
       <c r="P47" t="n">
-        <v>9.699999999999999</v>
+        <v>13.6</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
       </c>
       <c r="S47" t="n">
-        <v>0.05115509033203125</v>
+        <v>0.241060733795166</v>
       </c>
       <c r="T47" t="n">
-        <v>1.048267602920532</v>
+        <v>29.30585932731628</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -3535,56 +3627,58 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.1921397335565684</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>3.009137526091424e-155</v>
       </c>
       <c r="E48" t="n">
-        <v>0.3732731342315674</v>
+        <v>0.6365370154380798</v>
       </c>
       <c r="F48" t="n">
-        <v>18.17750000000001</v>
+        <v>17.07114348302301</v>
       </c>
       <c r="G48" t="n">
-        <v>0.1755888650963597</v>
+        <v>2.137044967880086</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
       <c r="K48" t="n">
         <v>0.5</v>
       </c>
       <c r="L48" t="n">
-        <v>0.2</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="M48" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.3798449612403101</v>
       </c>
       <c r="N48" t="n">
-        <v>2.222482442855835</v>
+        <v>26.36601758003235</v>
       </c>
       <c r="O48" t="n">
-        <v>1422.44140625</v>
+        <v>1428.2578125</v>
       </c>
       <c r="P48" t="n">
-        <v>9.300000000000001</v>
+        <v>14.7</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>0.0501246452331543</v>
+        <v>0.241774320602417</v>
       </c>
       <c r="T48" t="n">
-        <v>2.172355651855469</v>
+        <v>26.12423872947693</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -3600,56 +3694,58 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.1884816704235083</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>0.0251064416017619</v>
       </c>
       <c r="E49" t="n">
-        <v>0.3575944304466248</v>
+        <v>0.6036085486412048</v>
       </c>
       <c r="F49" t="n">
-        <v>18.17750000000001</v>
+        <v>31.76106283422462</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1579961464354528</v>
+        <v>1.310211946050096</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
       <c r="K49" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L49" t="n">
-        <v>0.2</v>
+        <v>0.2564102564102564</v>
       </c>
       <c r="M49" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2982456140350877</v>
       </c>
       <c r="N49" t="n">
-        <v>0.8767650127410889</v>
+        <v>25.7324275970459</v>
       </c>
       <c r="O49" t="n">
-        <v>1422.515625</v>
+        <v>1428.2734375</v>
       </c>
       <c r="P49" t="n">
-        <v>8.4</v>
+        <v>14.8</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>0.1152732372283936</v>
+        <v>0.2490670680999756</v>
       </c>
       <c r="T49" t="n">
-        <v>0.7614893913269043</v>
+        <v>25.48335790634155</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
@@ -3665,56 +3761,58 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.2042553144641015</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>0.01738780587599618</v>
       </c>
       <c r="E50" t="n">
-        <v>0.3559588491916656</v>
+        <v>0.6312508583068848</v>
       </c>
       <c r="F50" t="n">
-        <v>18.17750000000001</v>
+        <v>35.99870233246949</v>
       </c>
       <c r="G50" t="n">
-        <v>0.157088122605364</v>
+        <v>1.814176245210728</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
       <c r="K50" t="n">
         <v>0.5</v>
       </c>
       <c r="L50" t="n">
-        <v>0.2</v>
+        <v>0.2912621359223301</v>
       </c>
       <c r="M50" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.3286219081272085</v>
       </c>
       <c r="N50" t="n">
-        <v>1.342483520507812</v>
+        <v>32.11345148086548</v>
       </c>
       <c r="O50" t="n">
-        <v>1422.515625</v>
+        <v>1428.328125</v>
       </c>
       <c r="P50" t="n">
-        <v>10</v>
+        <v>14.4</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0.04998922348022461</v>
+        <v>0.2362794876098633</v>
       </c>
       <c r="T50" t="n">
-        <v>1.292491912841797</v>
+        <v>31.87716865539551</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
@@ -3730,56 +3828,58 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>0.2719033185925649</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>1.043540499499188e-78</v>
       </c>
       <c r="E51" t="n">
-        <v>0.3522716164588928</v>
+        <v>0.625874936580658</v>
       </c>
       <c r="F51" t="n">
-        <v>18.17750000000001</v>
+        <v>41.32096045197741</v>
       </c>
       <c r="G51" t="n">
-        <v>0.1091877496671105</v>
+        <v>1.754993342210386</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
       <c r="K51" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>0.2</v>
+        <v>0.2792207792207792</v>
       </c>
       <c r="M51" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.375</v>
       </c>
       <c r="N51" t="n">
-        <v>1.789185047149658</v>
+        <v>38.95255517959595</v>
       </c>
       <c r="O51" t="n">
-        <v>1422.55859375</v>
+        <v>1428.3828125</v>
       </c>
       <c r="P51" t="n">
-        <v>10.2</v>
+        <v>14.8</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0.05191898345947266</v>
+        <v>0.2860369682312012</v>
       </c>
       <c r="T51" t="n">
-        <v>1.737263441085815</v>
+        <v>38.66651153564453</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
@@ -3795,56 +3895,58 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.008368200347332884</v>
+        <v>0.217765038541884</v>
       </c>
       <c r="D52" t="n">
-        <v>1.337700353554117e-259</v>
+        <v>0.0128160358684791</v>
       </c>
       <c r="E52" t="n">
-        <v>0.3636881113052368</v>
+        <v>0.59571373462677</v>
       </c>
       <c r="F52" t="n">
-        <v>18.17750000000001</v>
+        <v>44.05383869011524</v>
       </c>
       <c r="G52" t="n">
-        <v>0.05946337926033358</v>
+        <v>0.5250181290790428</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
       <c r="K52" t="n">
         <v>1</v>
       </c>
       <c r="L52" t="n">
-        <v>0.2</v>
+        <v>0.1844660194174757</v>
       </c>
       <c r="M52" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.3852459016393442</v>
       </c>
       <c r="N52" t="n">
-        <v>1.112174272537231</v>
+        <v>22.05804204940796</v>
       </c>
       <c r="O52" t="n">
-        <v>1422.625</v>
+        <v>1428.390625</v>
       </c>
       <c r="P52" t="n">
-        <v>18.3</v>
+        <v>14.4</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0.05055522918701172</v>
+        <v>0.2756595611572266</v>
       </c>
       <c r="T52" t="n">
-        <v>1.061616897583008</v>
+        <v>21.78237915039062</v>
       </c>
       <c r="U52" t="n">
         <v>0</v>
@@ -3860,56 +3962,58 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>0.3625254534202198</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
+        <v>0.02733090230668268</v>
       </c>
       <c r="E53" t="n">
-        <v>0.3401545286178589</v>
+        <v>0.6716035604476929</v>
       </c>
       <c r="F53" t="n">
-        <v>18.17750000000001</v>
+        <v>42.40860518190365</v>
       </c>
       <c r="G53" t="n">
-        <v>0.04375667022411953</v>
+        <v>0.6488794023479189</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>0.2</v>
+        <v>0.270440251572327</v>
       </c>
       <c r="M53" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.4366197183098592</v>
       </c>
       <c r="N53" t="n">
-        <v>1.710916757583618</v>
+        <v>23.49525189399719</v>
       </c>
       <c r="O53" t="n">
-        <v>1422.765625</v>
+        <v>1428.40234375</v>
       </c>
       <c r="P53" t="n">
-        <v>18.7</v>
+        <v>13.5</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0.0487210750579834</v>
+        <v>0.2365756034851074</v>
       </c>
       <c r="T53" t="n">
-        <v>1.662192821502686</v>
+        <v>23.25867247581482</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -3925,56 +4029,58 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>0.1124497964458638</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
+        <v>4.652197395457911e-159</v>
       </c>
       <c r="E54" t="n">
-        <v>0.3295550942420959</v>
+        <v>0.5646926760673523</v>
       </c>
       <c r="F54" t="n">
-        <v>18.17750000000001</v>
+        <v>21.97300000000004</v>
       </c>
       <c r="G54" t="n">
-        <v>0.06033848417954378</v>
+        <v>0.2310522442972774</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
-      <c r="J54" t="inlineStr"/>
+      <c r="J54" t="n">
+        <v>1</v>
+      </c>
       <c r="K54" t="n">
         <v>0.5</v>
       </c>
       <c r="L54" t="n">
-        <v>0.2</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="M54" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.126984126984127</v>
       </c>
       <c r="N54" t="n">
-        <v>1.957052707672119</v>
+        <v>18.25840330123901</v>
       </c>
       <c r="O54" t="n">
-        <v>1422.7890625</v>
+        <v>1428.44921875</v>
       </c>
       <c r="P54" t="n">
-        <v>9.5</v>
+        <v>14.9</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>0.04836034774780273</v>
+        <v>0.2397184371948242</v>
       </c>
       <c r="T54" t="n">
-        <v>1.908689498901367</v>
+        <v>18.0186824798584</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
@@ -3990,56 +4096,58 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>0.06666666441015097</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
+        <v>3.80854569560441e-158</v>
       </c>
       <c r="E55" t="n">
-        <v>0.3474581241607666</v>
+        <v>0.5720757246017456</v>
       </c>
       <c r="F55" t="n">
-        <v>18.17750000000001</v>
+        <v>5.618909883720931</v>
       </c>
       <c r="G55" t="n">
-        <v>0.05304010349288486</v>
+        <v>0.2121604139715395</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>0.7894736842105263</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
       <c r="K55" t="n">
         <v>0.5</v>
       </c>
       <c r="L55" t="n">
-        <v>0.2</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="M55" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.2105263157894737</v>
       </c>
       <c r="N55" t="n">
-        <v>0.4313206672668457</v>
+        <v>24.1825840473175</v>
       </c>
       <c r="O55" t="n">
-        <v>1422.79296875</v>
+        <v>1428.44921875</v>
       </c>
       <c r="P55" t="n">
-        <v>8.699999999999999</v>
+        <v>14.9</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0.04838085174560547</v>
+        <v>0.2392697334289551</v>
       </c>
       <c r="T55" t="n">
-        <v>0.3829376697540283</v>
+        <v>23.94331240653992</v>
       </c>
       <c r="U55" t="n">
         <v>0</v>
@@ -4055,56 +4163,58 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>0.1780415391397301</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
+        <v>0.003004532769915607</v>
       </c>
       <c r="E56" t="n">
-        <v>0.3379605710506439</v>
+        <v>0.6103305816650391</v>
       </c>
       <c r="F56" t="n">
-        <v>18.17750000000001</v>
+        <v>27.8866727581256</v>
       </c>
       <c r="G56" t="n">
-        <v>0.05232929164007658</v>
+        <v>0.396936821952776</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
       <c r="K56" t="n">
         <v>1</v>
       </c>
       <c r="L56" t="n">
-        <v>0.2</v>
+        <v>0.2777777777777778</v>
       </c>
       <c r="M56" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.3452380952380952</v>
       </c>
       <c r="N56" t="n">
-        <v>1.150134563446045</v>
+        <v>28.07696628570557</v>
       </c>
       <c r="O56" t="n">
-        <v>1422.79296875</v>
+        <v>1428.453125</v>
       </c>
       <c r="P56" t="n">
-        <v>9</v>
+        <v>13.6</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0.04962730407714844</v>
+        <v>0.2880773544311523</v>
       </c>
       <c r="T56" t="n">
-        <v>1.100505352020264</v>
+        <v>27.78888702392578</v>
       </c>
       <c r="U56" t="n">
         <v>0</v>
@@ -4120,56 +4230,58 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0</v>
+        <v>0.100775191567514</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>8.833749696962384e-160</v>
       </c>
       <c r="E57" t="n">
-        <v>0.3721605241298676</v>
+        <v>0.5787584781646729</v>
       </c>
       <c r="F57" t="n">
-        <v>18.17750000000001</v>
+        <v>6.36324193548387</v>
       </c>
       <c r="G57" t="n">
-        <v>0.02825637491385252</v>
+        <v>0.1592005513439008</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0</v>
+      </c>
       <c r="K57" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L57" t="n">
-        <v>0.2</v>
+        <v>0.2203389830508475</v>
       </c>
       <c r="M57" t="n">
-        <v>0.04</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="N57" t="n">
-        <v>0.4090378284454346</v>
+        <v>22.16571664810181</v>
       </c>
       <c r="O57" t="n">
-        <v>1422.796875</v>
+        <v>1428.57421875</v>
       </c>
       <c r="P57" t="n">
-        <v>9.199999999999999</v>
+        <v>14.9</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0.05159854888916016</v>
+        <v>0.2532205581665039</v>
       </c>
       <c r="T57" t="n">
-        <v>0.3574364185333252</v>
+        <v>21.91249418258667</v>
       </c>
       <c r="U57" t="n">
         <v>0</v>
@@ -4185,56 +4297,58 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.01197604721144541</v>
+        <v>0.1791044744239004</v>
       </c>
       <c r="D58" t="n">
-        <v>7.209801557273821e-253</v>
+        <v>3.156456764334584e-157</v>
       </c>
       <c r="E58" t="n">
-        <v>0.3468083739280701</v>
+        <v>0.5300702452659607</v>
       </c>
       <c r="F58" t="n">
-        <v>18.17750000000001</v>
+        <v>23.95756410256416</v>
       </c>
       <c r="G58" t="n">
-        <v>0.08855291576673865</v>
+        <v>0.3002159827213823</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
       <c r="K58" t="n">
         <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>0.2</v>
+        <v>0.3125</v>
       </c>
       <c r="M58" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.1764705882352941</v>
       </c>
       <c r="N58" t="n">
-        <v>1.964935064315796</v>
+        <v>14.46353507041931</v>
       </c>
       <c r="O58" t="n">
-        <v>1422.8125</v>
+        <v>1428.65625</v>
       </c>
       <c r="P58" t="n">
-        <v>9.300000000000001</v>
+        <v>14.2</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0.05034136772155762</v>
+        <v>0.2409212589263916</v>
       </c>
       <c r="T58" t="n">
-        <v>1.91459059715271</v>
+        <v>14.22261095046997</v>
       </c>
       <c r="U58" t="n">
         <v>0</v>
@@ -4250,56 +4364,58 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0</v>
+        <v>0.09467455253807654</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>5.468024105341389e-233</v>
       </c>
       <c r="E59" t="n">
-        <v>0.3638429939746857</v>
+        <v>0.5583122968673706</v>
       </c>
       <c r="F59" t="n">
-        <v>18.17750000000001</v>
+        <v>7.75595785440612</v>
       </c>
       <c r="G59" t="n">
-        <v>0.1035353535353535</v>
+        <v>0.3939393939393939</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
-      <c r="J59" t="inlineStr"/>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
       <c r="K59" t="n">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="L59" t="n">
-        <v>0.2</v>
+        <v>0.3157894736842105</v>
       </c>
       <c r="M59" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="N59" t="n">
-        <v>0.514394998550415</v>
+        <v>15.82165861129761</v>
       </c>
       <c r="O59" t="n">
-        <v>1422.84765625</v>
+        <v>1428.75</v>
       </c>
       <c r="P59" t="n">
-        <v>8.6</v>
+        <v>12.6</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>0.05374026298522949</v>
+        <v>0.2703752517700195</v>
       </c>
       <c r="T59" t="n">
-        <v>0.4606523513793945</v>
+        <v>15.55128026008606</v>
       </c>
       <c r="U59" t="n">
         <v>0</v>
@@ -4315,56 +4431,58 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.004454342720720646</v>
+        <v>0.184501842032584</v>
       </c>
       <c r="D60" t="n">
-        <v>4.619442984542263e-300</v>
+        <v>0.0007467181732013424</v>
       </c>
       <c r="E60" t="n">
-        <v>0.3617115616798401</v>
+        <v>0.6244144439697266</v>
       </c>
       <c r="F60" t="n">
-        <v>18.17750000000001</v>
+        <v>-1.772625000000005</v>
       </c>
       <c r="G60" t="n">
-        <v>0.0286512928022362</v>
+        <v>0.2131376659678546</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
       <c r="K60" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L60" t="n">
-        <v>0.2</v>
+        <v>0.2875</v>
       </c>
       <c r="M60" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2753623188405797</v>
       </c>
       <c r="N60" t="n">
-        <v>1.0070481300354</v>
+        <v>19.068115234375</v>
       </c>
       <c r="O60" t="n">
-        <v>1422.8828125</v>
+        <v>1428.828125</v>
       </c>
       <c r="P60" t="n">
-        <v>8.800000000000001</v>
+        <v>15.4</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0.05050301551818848</v>
+        <v>0.2418711185455322</v>
       </c>
       <c r="T60" t="n">
-        <v>0.9565427303314209</v>
+        <v>18.82624125480652</v>
       </c>
       <c r="U60" t="n">
         <v>0</v>
@@ -4380,56 +4498,58 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0</v>
+        <v>0.1538461511671296</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
+        <v>5.21589699073297e-79</v>
       </c>
       <c r="E61" t="n">
-        <v>0.384681910276413</v>
+        <v>0.4778137505054474</v>
       </c>
       <c r="F61" t="n">
-        <v>18.17750000000001</v>
+        <v>44.61428571428573</v>
       </c>
       <c r="G61" t="n">
-        <v>0.3319838056680162</v>
+        <v>4.016194331983805</v>
       </c>
       <c r="H61" t="n">
         <v>1</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
       <c r="K61" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L61" t="n">
-        <v>0.2</v>
+        <v>0.2704918032786885</v>
       </c>
       <c r="M61" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.3478260869565217</v>
       </c>
       <c r="N61" t="n">
-        <v>1.330243349075317</v>
+        <v>23.78583002090454</v>
       </c>
       <c r="O61" t="n">
-        <v>1422.8984375</v>
+        <v>1428.8359375</v>
       </c>
       <c r="P61" t="n">
-        <v>9.1</v>
+        <v>14.9</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>0.04955029487609863</v>
+        <v>0.2427754402160645</v>
       </c>
       <c r="T61" t="n">
-        <v>1.280691146850586</v>
+        <v>23.54305171966553</v>
       </c>
       <c r="U61" t="n">
         <v>0</v>
@@ -4445,56 +4565,58 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0</v>
+        <v>0.1954022939800504</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
+        <v>7.063788090273745e-79</v>
       </c>
       <c r="E62" t="n">
-        <v>0.3322982490062714</v>
+        <v>0.632626473903656</v>
       </c>
       <c r="F62" t="n">
-        <v>18.17750000000001</v>
+        <v>42.91264214046828</v>
       </c>
       <c r="G62" t="n">
-        <v>0.205</v>
+        <v>1.6825</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
       <c r="K62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L62" t="n">
-        <v>0.2</v>
+        <v>0.2891566265060241</v>
       </c>
       <c r="M62" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.3467336683417085</v>
       </c>
       <c r="N62" t="n">
-        <v>1.064628839492798</v>
+        <v>19.27034783363342</v>
       </c>
       <c r="O62" t="n">
-        <v>1422.91015625</v>
+        <v>1428.8359375</v>
       </c>
       <c r="P62" t="n">
-        <v>9.5</v>
+        <v>12.7</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0.0484459400177002</v>
+        <v>0.2710907459259033</v>
       </c>
       <c r="T62" t="n">
-        <v>1.016180276870728</v>
+        <v>18.99925470352173</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
@@ -4510,56 +4632,58 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0</v>
+        <v>0.2445414798466849</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
+        <v>3.124656596953237e-155</v>
       </c>
       <c r="E63" t="n">
-        <v>0.3240036368370056</v>
+        <v>0.6403332948684692</v>
       </c>
       <c r="F63" t="n">
-        <v>18.17750000000001</v>
+        <v>60.93000000000004</v>
       </c>
       <c r="G63" t="n">
-        <v>0.1143654114365411</v>
+        <v>0.8633193863319386</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1</v>
+      </c>
       <c r="K63" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L63" t="n">
-        <v>0.2</v>
+        <v>0.4324324324324325</v>
       </c>
       <c r="M63" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.2753623188405797</v>
       </c>
       <c r="N63" t="n">
-        <v>0.5330078601837158</v>
+        <v>20.45079207420349</v>
       </c>
       <c r="O63" t="n">
-        <v>1422.96484375</v>
+        <v>1428.8359375</v>
       </c>
       <c r="P63" t="n">
-        <v>15.8</v>
+        <v>15.3</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0.0521705150604248</v>
+        <v>0.2729942798614502</v>
       </c>
       <c r="T63" t="n">
-        <v>0.4808344841003418</v>
+        <v>20.17779445648193</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
@@ -4575,56 +4699,58 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
+        <v>0.2753036387844417</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>4.316577219300353e-155</v>
       </c>
       <c r="E64" t="n">
-        <v>0.3228385746479034</v>
+        <v>0.6672869324684143</v>
       </c>
       <c r="F64" t="n">
-        <v>18.17750000000001</v>
+        <v>56.20788927335641</v>
       </c>
       <c r="G64" t="n">
-        <v>0.1344262295081967</v>
+        <v>1.431147540983607</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
-      </c>
-      <c r="J64" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
       <c r="K64" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L64" t="n">
-        <v>0.2</v>
+        <v>0.3425925925925926</v>
       </c>
       <c r="M64" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.3636363636363636</v>
       </c>
       <c r="N64" t="n">
-        <v>0.6343700885772705</v>
+        <v>27.08725309371948</v>
       </c>
       <c r="O64" t="n">
-        <v>1423.01171875</v>
+        <v>1428.8359375</v>
       </c>
       <c r="P64" t="n">
-        <v>18.4</v>
+        <v>14.7</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0.0495448112487793</v>
+        <v>0.2595696449279785</v>
       </c>
       <c r="T64" t="n">
-        <v>0.5848231315612793</v>
+        <v>26.82768082618713</v>
       </c>
       <c r="U64" t="n">
         <v>0</v>
@@ -4640,56 +4766,58 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0</v>
+        <v>0.2762430889301304</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
+        <v>9.780277285639061e-79</v>
       </c>
       <c r="E65" t="n">
-        <v>0.3265484273433685</v>
+        <v>0.6209030747413635</v>
       </c>
       <c r="F65" t="n">
-        <v>18.17750000000001</v>
+        <v>35.98593023255816</v>
       </c>
       <c r="G65" t="n">
-        <v>0.1643286573146293</v>
+        <v>1.158316633266533</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J65" t="n">
+        <v>1</v>
+      </c>
       <c r="K65" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L65" t="n">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="M65" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="N65" t="n">
-        <v>0.5355420112609863</v>
+        <v>17.49422287940979</v>
       </c>
       <c r="O65" t="n">
-        <v>1423.03125</v>
+        <v>1428.8359375</v>
       </c>
       <c r="P65" t="n">
-        <v>18.3</v>
+        <v>13</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0.05477666854858398</v>
+        <v>0.2382171154022217</v>
       </c>
       <c r="T65" t="n">
-        <v>0.4807629585266113</v>
+        <v>17.25600385665894</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
@@ -4705,56 +4833,58 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0</v>
+        <v>0.298136640995332</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
+        <v>0.0571884361243411</v>
       </c>
       <c r="E66" t="n">
-        <v>0.3350982666015625</v>
+        <v>0.714253842830658</v>
       </c>
       <c r="F66" t="n">
-        <v>18.17750000000001</v>
+        <v>40.53819964349378</v>
       </c>
       <c r="G66" t="n">
-        <v>0.1028858218318695</v>
+        <v>1.409033877038896</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J66" t="n">
+        <v>1</v>
+      </c>
       <c r="K66" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L66" t="n">
-        <v>0.2</v>
+        <v>0.3306451612903226</v>
       </c>
       <c r="M66" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.4642857142857143</v>
       </c>
       <c r="N66" t="n">
-        <v>1.633043050765991</v>
+        <v>26.71403932571411</v>
       </c>
       <c r="O66" t="n">
-        <v>1423.03515625</v>
+        <v>1428.8359375</v>
       </c>
       <c r="P66" t="n">
-        <v>17.7</v>
+        <v>14.9</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
       <c r="S66" t="n">
-        <v>0.0508263111114502</v>
+        <v>0.2412741184234619</v>
       </c>
       <c r="T66" t="n">
-        <v>1.582214593887329</v>
+        <v>26.4727623462677</v>
       </c>
       <c r="U66" t="n">
         <v>0</v>
@@ -4770,56 +4900,58 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0</v>
+        <v>0.2166064932236835</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
+        <v>3.084116923537544e-155</v>
       </c>
       <c r="E67" t="n">
-        <v>0.3333593308925629</v>
+        <v>0.6865761280059814</v>
       </c>
       <c r="F67" t="n">
-        <v>18.17750000000001</v>
+        <v>41.6782156019656</v>
       </c>
       <c r="G67" t="n">
-        <v>0.1123287671232877</v>
+        <v>1.305479452054795</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J67" t="n">
+        <v>1</v>
+      </c>
       <c r="K67" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>0.2</v>
+        <v>0.287037037037037</v>
       </c>
       <c r="M67" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.3893129770992366</v>
       </c>
       <c r="N67" t="n">
-        <v>1.263818025588989</v>
+        <v>31.29414844512939</v>
       </c>
       <c r="O67" t="n">
-        <v>1423.0390625</v>
+        <v>1428.87890625</v>
       </c>
       <c r="P67" t="n">
-        <v>9</v>
+        <v>14.7</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
       <c r="S67" t="n">
-        <v>0.05042791366577148</v>
+        <v>0.2420082092285156</v>
       </c>
       <c r="T67" t="n">
-        <v>1.213387727737427</v>
+        <v>31.05213713645935</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
@@ -4835,56 +4967,58 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0</v>
+        <v>0.05882352864179703</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
+        <v>6.577771803681657e-232</v>
       </c>
       <c r="E68" t="n">
-        <v>0.4337139129638672</v>
+        <v>0.4336404800415039</v>
       </c>
       <c r="F68" t="n">
-        <v>18.17750000000001</v>
+        <v>22.42743968208916</v>
       </c>
       <c r="G68" t="n">
-        <v>0.6456692913385826</v>
+        <v>19.34645669291339</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="J68" t="n">
+        <v>1</v>
+      </c>
       <c r="K68" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L68" t="n">
-        <v>0.2</v>
+        <v>0.2388059701492537</v>
       </c>
       <c r="M68" t="n">
-        <v>0.2</v>
+        <v>0.7324414715719063</v>
       </c>
       <c r="N68" t="n">
-        <v>0.4204361438751221</v>
+        <v>54.51508378982544</v>
       </c>
       <c r="O68" t="n">
-        <v>1423.05078125</v>
+        <v>1428.9765625</v>
       </c>
       <c r="P68" t="n">
-        <v>8.699999999999999</v>
+        <v>14.3</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
       <c r="S68" t="n">
-        <v>0.04936838150024414</v>
+        <v>0.2401511669158936</v>
       </c>
       <c r="T68" t="n">
-        <v>0.3710649013519287</v>
+        <v>54.2749297618866</v>
       </c>
       <c r="U68" t="n">
         <v>0</v>
